--- a/docs/EN/EN_TakaPlast_Budget.xlsx
+++ b/docs/EN/EN_TakaPlast_Budget.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="447" documentId="11_6A32D4F240207C91FB7A9A1550F542CAE46E6FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69B91B92-DAB2-4FA6-86B2-B4AD10E0BDA1}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="11_6A32D4F240207C91FB7A9A1550F542CAE46E6FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81777FA6-0CBC-449A-8D93-AFF8835B1641}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="914">
   <si>
     <t>TAKAPLAST — SUMMARY</t>
   </si>
@@ -1600,7 +1600,16 @@
     <t>Sales</t>
   </si>
   <si>
-    <t>B2B Sales Representatives</t>
+    <t>B2B Sales Industry / Energy</t>
+  </si>
+  <si>
+    <t>B2B Sales BPT</t>
+  </si>
+  <si>
+    <t>B2B Sales Distribution / Resellers</t>
+  </si>
+  <si>
+    <t>Sales Multipurpose Land</t>
   </si>
   <si>
     <t>OPERATIONS</t>
@@ -2959,7 +2968,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -3034,11 +3043,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3218,14 +3257,14 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3239,6 +3278,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4107,7 +4148,7 @@
       </c>
       <c r="B5" s="2">
         <f>CAPEX_Consolidated!B19</f>
-        <v>2312596.8833333338</v>
+        <v>2360476.8833333338</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
@@ -4119,7 +4160,7 @@
       </c>
       <c r="B6" s="5">
         <f>CAPEX_Consolidated!B20</f>
-        <v>8437966.4833333343</v>
+        <v>8485846.4833333343</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
@@ -4277,7 +4318,7 @@
       </c>
       <c r="B24" s="2">
         <f>OPEX_Operations!D53</f>
-        <v>1791995</v>
+        <v>1837139</v>
       </c>
       <c r="C24" s="3"/>
     </row>
@@ -4287,7 +4328,7 @@
       </c>
       <c r="B25" s="2">
         <f>OPEX_Operations!E53</f>
-        <v>3295700.6</v>
+        <v>3365468.6</v>
       </c>
       <c r="C25" s="3"/>
     </row>
@@ -4297,7 +4338,7 @@
       </c>
       <c r="B26" s="2">
         <f>OPEX_Operations!F53</f>
-        <v>3964451.8000000003</v>
+        <v>4046531.8000000003</v>
       </c>
       <c r="C26" s="3"/>
     </row>
@@ -4307,7 +4348,7 @@
       </c>
       <c r="B27" s="2">
         <f>OPEX_Operations!G53</f>
-        <v>4015920</v>
+        <v>4098000</v>
       </c>
       <c r="C27" s="3"/>
     </row>
@@ -4317,7 +4358,7 @@
       </c>
       <c r="B28" s="2">
         <f>OPEX_Operations!H53</f>
-        <v>4035920</v>
+        <v>4118000</v>
       </c>
       <c r="C28" s="3"/>
     </row>
@@ -4332,7 +4373,7 @@
       </c>
       <c r="B30" s="2">
         <f>Revenue!E21</f>
-        <v>8005</v>
+        <v>-37139</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -4342,7 +4383,7 @@
       </c>
       <c r="B31" s="2">
         <f>Revenue!F21</f>
-        <v>6184299.4000000004</v>
+        <v>6114531.4000000004</v>
       </c>
       <c r="C31" s="3"/>
     </row>
@@ -4352,7 +4393,7 @@
       </c>
       <c r="B32" s="2">
         <f>Revenue!G21</f>
-        <v>7675548.1999999993</v>
+        <v>7593468.1999999993</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>32</v>
@@ -4364,7 +4405,7 @@
       </c>
       <c r="B33" s="2">
         <f>Revenue!H21</f>
-        <v>7984080</v>
+        <v>7902000</v>
       </c>
       <c r="C33" s="3"/>
     </row>
@@ -4374,7 +4415,7 @@
       </c>
       <c r="B34" s="2">
         <f>Revenue!I21</f>
-        <v>7964080</v>
+        <v>7882000</v>
       </c>
       <c r="C34" s="3"/>
     </row>
@@ -4648,28 +4689,28 @@
         <v>59</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>72</v>
@@ -4677,7 +4718,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="78" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -4698,10 +4739,10 @@
         <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E3" s="2">
         <f>Assumptions!B40*Assumptions!B30</f>
@@ -4727,7 +4768,7 @@
         <v>0.48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4735,13 +4776,13 @@
         <v>263</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E4" s="2">
         <f>Assumptions!B41*Assumptions!B30</f>
@@ -4767,7 +4808,7 @@
         <v>0.45</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4775,13 +4816,13 @@
         <v>239</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E5" s="2">
         <f>Assumptions!B42*Assumptions!B30</f>
@@ -4807,13 +4848,13 @@
         <v>0.52</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="17"/>
       <c r="B6" s="17" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -4842,7 +4883,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="78" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B8" s="78"/>
       <c r="C8" s="78"/>
@@ -4858,10 +4899,10 @@
     <row r="9" spans="1:11">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2">
@@ -4886,16 +4927,16 @@
         <v>86</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="2">
@@ -4921,16 +4962,16 @@
         <v>45</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2">
@@ -4954,13 +4995,13 @@
         <v>38</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>169</v>
@@ -4987,16 +5028,16 @@
         <v>65</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2">
@@ -5019,13 +5060,13 @@
         <v>75</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -5055,7 +5096,7 @@
     <row r="16" spans="1:11">
       <c r="A16" s="35"/>
       <c r="B16" s="35" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
@@ -5084,7 +5125,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="78" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B18" s="78"/>
       <c r="C18" s="78"/>
@@ -5100,7 +5141,7 @@
     <row r="19" spans="1:11">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -5130,29 +5171,29 @@
     <row r="20" spans="1:11">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="43">
         <f>OPEX_Operations!D53</f>
-        <v>1791995</v>
+        <v>1837139</v>
       </c>
       <c r="F20" s="43">
         <f>OPEX_Operations!E53</f>
-        <v>3295700.6</v>
+        <v>3365468.6</v>
       </c>
       <c r="G20" s="43">
         <f>OPEX_Operations!F53</f>
-        <v>3964451.8000000003</v>
+        <v>4046531.8000000003</v>
       </c>
       <c r="H20" s="43">
         <f>OPEX_Operations!G53</f>
-        <v>4015920</v>
+        <v>4098000</v>
       </c>
       <c r="I20" s="43">
         <f>OPEX_Operations!H53</f>
-        <v>4035920</v>
+        <v>4118000</v>
       </c>
       <c r="J20" s="43"/>
       <c r="K20" s="11"/>
@@ -5160,29 +5201,29 @@
     <row r="21" spans="1:11">
       <c r="A21" s="35"/>
       <c r="B21" s="35" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
       <c r="E21" s="37">
         <f>E19-E20</f>
-        <v>8005</v>
+        <v>-37139</v>
       </c>
       <c r="F21" s="37">
         <f>F19-F20</f>
-        <v>6184299.4000000004</v>
+        <v>6114531.4000000004</v>
       </c>
       <c r="G21" s="37">
         <f>G19-G20</f>
-        <v>7675548.1999999993</v>
+        <v>7593468.1999999993</v>
       </c>
       <c r="H21" s="37">
         <f>H19-H20</f>
-        <v>7984080</v>
+        <v>7902000</v>
       </c>
       <c r="I21" s="37">
         <f>I19-I20</f>
-        <v>7964080</v>
+        <v>7882000</v>
       </c>
       <c r="J21" s="37"/>
       <c r="K21" s="36"/>
@@ -5190,29 +5231,29 @@
     <row r="22" spans="1:11">
       <c r="A22" s="44"/>
       <c r="B22" s="44" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="45"/>
       <c r="E22" s="55">
         <f>IF(E19=0,0,E21/E19)</f>
-        <v>4.4472222222222222E-3</v>
+        <v>-2.0632777777777778E-2</v>
       </c>
       <c r="F22" s="55">
         <f>IF(F19=0,0,F21/F19)</f>
-        <v>0.65235225738396629</v>
+        <v>0.64499276371308023</v>
       </c>
       <c r="G22" s="55">
         <f>IF(G19=0,0,G21/G19)</f>
-        <v>0.65941135738831613</v>
+        <v>0.65235981099656348</v>
       </c>
       <c r="H22" s="55">
         <f>IF(H19=0,0,H21/H19)</f>
-        <v>0.66534000000000004</v>
+        <v>0.65849999999999997</v>
       </c>
       <c r="I22" s="55">
         <f>IF(I19=0,0,I21/I19)</f>
-        <v>0.66367333333333334</v>
+        <v>0.65683333333333338</v>
       </c>
       <c r="J22" s="55"/>
       <c r="K22" s="45"/>
@@ -5247,33 +5288,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="78" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -5285,190 +5326,190 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="9" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C3" s="43">
         <v>600000</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="9" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C4" s="43">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C5" s="43">
         <v>500000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="9" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C6" s="43">
         <v>150000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="9" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C7" s="43">
         <v>500000</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C8" s="43">
         <v>500000</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="9" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C9" s="43">
         <v>300000</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C10" s="34">
         <v>2800000</v>
@@ -5481,7 +5522,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="78" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B11" s="78"/>
       <c r="C11" s="78"/>
@@ -5493,112 +5534,112 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="9" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C12" s="43">
         <v>500000</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="9" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C13" s="43">
         <v>200000</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C14" s="43">
         <v>300000</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="9" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C15" s="43">
         <v>1000000</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="17"/>
       <c r="B16" s="17" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C16" s="34">
         <v>2000000</v>
@@ -5611,7 +5652,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="78" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B17" s="78"/>
       <c r="C17" s="78"/>
@@ -5623,86 +5664,86 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C18" s="43">
         <v>200000</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="9" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C19" s="43">
         <v>100000</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="9" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C20" s="43">
         <v>50000</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>436</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="17"/>
       <c r="B21" s="17" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C21" s="34">
         <v>350000</v>
@@ -5716,7 +5757,7 @@
     <row r="23" spans="1:8">
       <c r="A23" s="35"/>
       <c r="B23" s="35" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C23" s="37">
         <f>C10+C16+C21</f>
@@ -5729,9 +5770,9 @@
       <c r="H23" s="36"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
-      <c r="A25" s="73"/>
+      <c r="A25" s="75"/>
       <c r="B25" s="83" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C25" s="83"/>
       <c r="D25" s="83"/>
@@ -6420,28 +6461,28 @@
       <c r="A52" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B52" s="74">
+      <c r="B52" s="73">
         <v>0.05</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="75" t="s">
+      <c r="D52" s="74" t="s">
         <v>172</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A43:D43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6746,7 +6787,7 @@
       </c>
       <c r="B19" s="27">
         <f>Working_Capital!G35</f>
-        <v>2312596.8833333338</v>
+        <v>2360476.8833333338</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28" t="s">
@@ -6762,7 +6803,7 @@
       </c>
       <c r="B20" s="30">
         <f>B17+B19</f>
-        <v>8437966.4833333343</v>
+        <v>8485846.4833333343</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -9749,16 +9790,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A72:H72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9770,7 +9811,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -10663,30 +10704,30 @@
         <v>518</v>
       </c>
       <c r="C28" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="40">
         <v>2000</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="84">
         <f>C28*D28*12</f>
-        <v>48000</v>
-      </c>
-      <c r="F28" s="2">
+        <v>24000</v>
+      </c>
+      <c r="F28" s="84">
         <f>E28*Assumptions!B37</f>
+        <v>6000</v>
+      </c>
+      <c r="G28" s="84">
+        <f>E28*0.05</f>
+        <v>1200</v>
+      </c>
+      <c r="H28" s="84">
+        <f>E28*0.5</f>
         <v>12000</v>
-      </c>
-      <c r="G28" s="2">
-        <f>E28*0.05</f>
-        <v>2400</v>
-      </c>
-      <c r="H28" s="2">
-        <f>E28*0.5</f>
-        <v>24000</v>
       </c>
       <c r="I28" s="2">
         <f>E28+F28+G28+H28</f>
-        <v>86400</v>
+        <v>43200</v>
       </c>
       <c r="J28" s="38" t="s">
         <v>501</v>
@@ -10696,425 +10737,471 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="C29" s="41">
-        <f>SUM(C28:C28)</f>
-        <v>2</v>
-      </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="34">
-        <f>SUM(I28:I28)</f>
-        <v>86400</v>
-      </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
+      <c r="A29" s="38" t="s">
+        <v>517</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>519</v>
+      </c>
+      <c r="C29" s="39">
+        <v>1</v>
+      </c>
+      <c r="D29" s="40">
+        <v>2000</v>
+      </c>
+      <c r="E29" s="84">
+        <f>C29*D29*12</f>
+        <v>24000</v>
+      </c>
+      <c r="F29" s="84">
+        <f>E29*Assumptions!B37</f>
+        <v>6000</v>
+      </c>
+      <c r="G29" s="84">
+        <f>E29*0.05</f>
+        <v>1200</v>
+      </c>
+      <c r="H29" s="84">
+        <f>E29*0.5</f>
+        <v>12000</v>
+      </c>
+      <c r="I29" s="2">
+        <f>E29+F29+G29+H29</f>
+        <v>43200</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="78" t="s">
-        <v>519</v>
-      </c>
-      <c r="B30" s="78"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
+      <c r="A30" s="38" t="s">
+        <v>517</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>520</v>
+      </c>
+      <c r="C30" s="39">
+        <v>1</v>
+      </c>
+      <c r="D30" s="40">
+        <v>2000</v>
+      </c>
+      <c r="E30" s="85">
+        <f>C30*D30*12</f>
+        <v>24000</v>
+      </c>
+      <c r="F30" s="85">
+        <f>E30*Assumptions!B37</f>
+        <v>6000</v>
+      </c>
+      <c r="G30" s="85">
+        <f>E30*0.05</f>
+        <v>1200</v>
+      </c>
+      <c r="H30" s="85">
+        <f>E30*0.5</f>
+        <v>12000</v>
+      </c>
+      <c r="I30" s="2">
+        <f>E30+F30+G30+H30</f>
+        <v>43200</v>
+      </c>
+      <c r="J30" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="38" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B31" s="38" t="s">
         <v>521</v>
       </c>
       <c r="C31" s="39">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D31" s="40">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E31" s="2">
-        <f>C31*D31*12</f>
-        <v>180000</v>
+        <f t="shared" ref="E31" si="0">C31*D31*12</f>
+        <v>21600</v>
       </c>
       <c r="F31" s="2">
         <f>E31*Assumptions!B37</f>
-        <v>45000</v>
+        <v>5400</v>
       </c>
       <c r="G31" s="2">
         <f>E31*0.05</f>
-        <v>9000</v>
-      </c>
-      <c r="H31" s="40">
-        <v>0</v>
+        <v>1080</v>
+      </c>
+      <c r="H31" s="2">
+        <f>E31*0.5</f>
+        <v>10800</v>
       </c>
       <c r="I31" s="2">
-        <f>E31+F31+G31+H31</f>
-        <v>234000</v>
+        <f t="shared" ref="I30:I31" si="1">E31+F31+G31+H31</f>
+        <v>38880</v>
       </c>
       <c r="J31" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>465</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="38" t="s">
-        <v>520</v>
-      </c>
-      <c r="B32" s="38" t="s">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C32" s="41">
+        <f>SUM(C28:C31)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="34">
+        <f>SUM(I28:I31)</f>
+        <v>168480</v>
+      </c>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="78" t="s">
         <v>522</v>
       </c>
-      <c r="C32" s="39">
-        <v>5</v>
-      </c>
-      <c r="D32" s="40">
-        <v>1500</v>
-      </c>
-      <c r="E32" s="2">
-        <f>C32*D32*12</f>
-        <v>90000</v>
-      </c>
-      <c r="F32" s="2">
-        <f>E32*Assumptions!B37</f>
-        <v>22500</v>
-      </c>
-      <c r="G32" s="2">
-        <f>E32*0.05</f>
-        <v>4500</v>
-      </c>
-      <c r="H32" s="40">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <f>E32+F32+G32+H32</f>
-        <v>117000</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>501</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="38" t="s">
-        <v>520</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>523</v>
-      </c>
-      <c r="C33" s="39">
-        <v>3</v>
-      </c>
-      <c r="D33" s="40">
-        <v>1200</v>
-      </c>
-      <c r="E33" s="2">
-        <f>C33*D33*12</f>
-        <v>43200</v>
-      </c>
-      <c r="F33" s="2">
-        <f>E33*Assumptions!B37</f>
-        <v>10800</v>
-      </c>
-      <c r="G33" s="2">
-        <f>E33*0.05</f>
-        <v>2160</v>
-      </c>
-      <c r="H33" s="40">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
-        <f>E33+F33+G33+H33</f>
-        <v>56160</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>501</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>504</v>
-      </c>
+      <c r="B33" s="78"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="78"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="38" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B34" s="38" t="s">
         <v>524</v>
       </c>
       <c r="C34" s="39">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D34" s="40">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E34" s="2">
         <f>C34*D34*12</f>
-        <v>18000</v>
+        <v>180000</v>
       </c>
       <c r="F34" s="2">
         <f>E34*Assumptions!B37</f>
-        <v>4500</v>
+        <v>45000</v>
       </c>
       <c r="G34" s="2">
         <f>E34*0.05</f>
-        <v>900</v>
+        <v>9000</v>
       </c>
       <c r="H34" s="40">
         <v>0</v>
       </c>
       <c r="I34" s="2">
         <f>E34+F34+G34+H34</f>
-        <v>23400</v>
+        <v>234000</v>
       </c>
       <c r="J34" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>504</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="38" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B35" s="38" t="s">
         <v>525</v>
       </c>
       <c r="C35" s="39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" s="40">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="2">
         <f>C35*D35*12</f>
-        <v>28800</v>
+        <v>90000</v>
       </c>
       <c r="F35" s="2">
         <f>E35*Assumptions!B37</f>
-        <v>7200</v>
+        <v>22500</v>
       </c>
       <c r="G35" s="2">
         <f>E35*0.05</f>
-        <v>1440</v>
+        <v>4500</v>
       </c>
       <c r="H35" s="40">
         <v>0</v>
       </c>
       <c r="I35" s="2">
         <f>E35+F35+G35+H35</f>
-        <v>37440</v>
+        <v>117000</v>
       </c>
       <c r="J35" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>370</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="38" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>526</v>
       </c>
       <c r="C36" s="39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="40">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E36" s="2">
         <f>C36*D36*12</f>
-        <v>24000</v>
+        <v>43200</v>
       </c>
       <c r="F36" s="2">
         <f>E36*Assumptions!B37</f>
-        <v>6000</v>
+        <v>10800</v>
       </c>
       <c r="G36" s="2">
         <f>E36*0.05</f>
-        <v>1200</v>
+        <v>2160</v>
       </c>
       <c r="H36" s="40">
         <v>0</v>
       </c>
       <c r="I36" s="2">
         <f>E36+F36+G36+H36</f>
-        <v>31200</v>
+        <v>56160</v>
       </c>
       <c r="J36" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>321</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="38" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B37" s="38" t="s">
         <v>527</v>
       </c>
       <c r="C37" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="40">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="E37" s="2">
         <f>C37*D37*12</f>
-        <v>9600</v>
+        <v>18000</v>
       </c>
       <c r="F37" s="2">
         <f>E37*Assumptions!B37</f>
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="G37" s="2">
         <f>E37*0.05</f>
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="H37" s="40">
         <v>0</v>
       </c>
       <c r="I37" s="2">
         <f>E37+F37+G37+H37</f>
-        <v>12480</v>
+        <v>23400</v>
       </c>
       <c r="J37" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>370</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="38" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B38" s="38" t="s">
         <v>528</v>
       </c>
       <c r="C38" s="39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" s="40">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E38" s="2">
         <f>C38*D38*12</f>
-        <v>18000</v>
+        <v>28800</v>
       </c>
       <c r="F38" s="2">
         <f>E38*Assumptions!B37</f>
-        <v>4500</v>
+        <v>7200</v>
       </c>
       <c r="G38" s="2">
         <f>E38*0.05</f>
-        <v>900</v>
+        <v>1440</v>
       </c>
       <c r="H38" s="40">
         <v>0</v>
       </c>
       <c r="I38" s="2">
         <f>E38+F38+G38+H38</f>
-        <v>23400</v>
+        <v>37440</v>
       </c>
       <c r="J38" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="C39" s="41">
-        <f>SUM(C31:C38)</f>
-        <v>44</v>
-      </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="34">
-        <f>SUM(I31:I38)</f>
-        <v>535080</v>
-      </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
+      <c r="A39" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>529</v>
+      </c>
+      <c r="C39" s="39">
+        <v>4</v>
+      </c>
+      <c r="D39" s="40">
+        <v>500</v>
+      </c>
+      <c r="E39" s="2">
+        <f>C39*D39*12</f>
+        <v>24000</v>
+      </c>
+      <c r="F39" s="2">
+        <f>E39*Assumptions!B37</f>
+        <v>6000</v>
+      </c>
+      <c r="G39" s="2">
+        <f>E39*0.05</f>
+        <v>1200</v>
+      </c>
+      <c r="H39" s="40">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <f>E39+F39+G39+H39</f>
+        <v>31200</v>
+      </c>
+      <c r="J39" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="K39" s="38" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="78" t="s">
-        <v>529</v>
-      </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
+      <c r="A40" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>530</v>
+      </c>
+      <c r="C40" s="39">
+        <v>2</v>
+      </c>
+      <c r="D40" s="40">
+        <v>400</v>
+      </c>
+      <c r="E40" s="2">
+        <f>C40*D40*12</f>
+        <v>9600</v>
+      </c>
+      <c r="F40" s="2">
+        <f>E40*Assumptions!B37</f>
+        <v>2400</v>
+      </c>
+      <c r="G40" s="2">
+        <f>E40*0.05</f>
+        <v>480</v>
+      </c>
+      <c r="H40" s="40">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <f>E40+F40+G40+H40</f>
+        <v>12480</v>
+      </c>
+      <c r="J40" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="K40" s="38" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="38" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B41" s="38" t="s">
         <v>531</v>
       </c>
       <c r="C41" s="39">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D41" s="40">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="E41" s="2">
         <f>C41*D41*12</f>
-        <v>180000</v>
-      </c>
-      <c r="F41" s="40">
-        <v>0</v>
+        <v>18000</v>
+      </c>
+      <c r="F41" s="2">
+        <f>E41*Assumptions!B37</f>
+        <v>4500</v>
       </c>
       <c r="G41" s="2">
         <f>E41*0.05</f>
-        <v>9000</v>
+        <v>900</v>
       </c>
       <c r="H41" s="40">
         <v>0</v>
       </c>
       <c r="I41" s="2">
         <f>E41+F41+G41+H41</f>
-        <v>189000</v>
+        <v>23400</v>
       </c>
       <c r="J41" s="38" t="s">
         <v>501</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>532</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -11123,8 +11210,8 @@
         <v>497</v>
       </c>
       <c r="C42" s="41">
-        <f>SUM(C41:C41)</f>
-        <v>50</v>
+        <f>SUM(C34:C41)</f>
+        <v>44</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19"/>
@@ -11132,47 +11219,121 @@
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
       <c r="I42" s="34">
-        <f>SUM(I41:I41)</f>
-        <v>189000</v>
+        <f>SUM(I34:I41)</f>
+        <v>535080</v>
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="78" t="s">
+        <v>532</v>
+      </c>
+      <c r="B43" s="78"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+    </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="35"/>
-      <c r="B44" s="35" t="s">
+      <c r="A44" s="38" t="s">
         <v>533</v>
       </c>
-      <c r="C44" s="42">
-        <f>C10+C18+C22+C26+C29+C39+C42</f>
-        <v>114</v>
-      </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="37">
-        <f>I10+I18+I22+I26+I29+I39+I42</f>
-        <v>2246280</v>
-      </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="62" t="s">
+      <c r="B44" s="38" t="s">
         <v>534</v>
       </c>
+      <c r="C44" s="39">
+        <v>50</v>
+      </c>
+      <c r="D44" s="40">
+        <v>300</v>
+      </c>
+      <c r="E44" s="2">
+        <f>C44*D44*12</f>
+        <v>180000</v>
+      </c>
+      <c r="F44" s="40">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <f>E44*0.05</f>
+        <v>9000</v>
+      </c>
+      <c r="H44" s="40">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <f>E44+F44+G44+H44</f>
+        <v>189000</v>
+      </c>
+      <c r="J44" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="K44" s="38" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C45" s="41">
+        <f>SUM(C44:C44)</f>
+        <v>50</v>
+      </c>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="34">
+        <f>SUM(I44:I44)</f>
+        <v>189000</v>
+      </c>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="62" t="s">
-        <v>535</v>
+      <c r="A47" s="35"/>
+      <c r="B47" s="35" t="s">
+        <v>536</v>
+      </c>
+      <c r="C47" s="42">
+        <f>C10+C18+C22+C26+C32+C42+C45</f>
+        <v>116</v>
+      </c>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="37">
+        <f>I10+I18+I22+I26+I32+I42+I45</f>
+        <v>2328360</v>
+      </c>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="62" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="62" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A19:K19"/>
@@ -11204,25 +11365,25 @@
         <v>306</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>72</v>
@@ -11230,7 +11391,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="78" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -11243,67 +11404,67 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D3" s="43">
-        <f>OPEX_HR!I44*0.55</f>
-        <v>1235454</v>
+        <f>OPEX_HR!I47*0.55</f>
+        <v>1280598</v>
       </c>
       <c r="E3" s="43">
-        <f>OPEX_HR!I44*0.85</f>
-        <v>1909338</v>
+        <f>OPEX_HR!I47*0.85</f>
+        <v>1979106</v>
       </c>
       <c r="F3" s="43">
-        <f>OPEX_HR!I44*1</f>
-        <v>2246280</v>
+        <f>OPEX_HR!I47*1</f>
+        <v>2328360</v>
       </c>
       <c r="G3" s="43">
-        <f>OPEX_HR!I44*1</f>
-        <v>2246280</v>
+        <f>OPEX_HR!I47*1</f>
+        <v>2328360</v>
       </c>
       <c r="H3" s="43">
-        <f>OPEX_HR!I44*1</f>
-        <v>2246280</v>
+        <f>OPEX_HR!I47*1</f>
+        <v>2328360</v>
       </c>
       <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="34">
         <f>D3</f>
-        <v>1235454</v>
+        <v>1280598</v>
       </c>
       <c r="E4" s="34">
         <f>E3</f>
-        <v>1909338</v>
+        <v>1979106</v>
       </c>
       <c r="F4" s="34">
         <f>F3</f>
-        <v>2246280</v>
+        <v>2328360</v>
       </c>
       <c r="G4" s="34">
         <f>G3</f>
-        <v>2246280</v>
+        <v>2328360</v>
       </c>
       <c r="H4" s="34">
         <f>H3</f>
-        <v>2246280</v>
+        <v>2328360</v>
       </c>
       <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="78" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B5" s="78"/>
       <c r="C5" s="78"/>
@@ -11316,13 +11477,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D6" s="2">
         <f>Assumptions!B10*Assumptions!B30</f>
@@ -11348,13 +11509,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D7" s="2">
         <f>Assumptions!B20*Assumptions!B30</f>
@@ -11380,10 +11541,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>182</v>
@@ -11407,13 +11568,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D9" s="2">
         <v>44000</v>
@@ -11434,13 +11595,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D10" s="2">
         <v>18000</v>
@@ -11462,7 +11623,7 @@
     <row r="11" spans="1:9">
       <c r="A11" s="17"/>
       <c r="B11" s="17" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="34">
@@ -11502,13 +11663,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D13" s="2">
         <f>Assumptions!B16*Assumptions!B30</f>
@@ -11535,7 +11696,7 @@
     <row r="14" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="34">
@@ -11562,7 +11723,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="78" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B15" s="78"/>
       <c r="C15" s="78"/>
@@ -11575,10 +11736,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2">
@@ -11605,10 +11766,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2">
@@ -11635,10 +11796,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2">
@@ -11660,10 +11821,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2">
@@ -11685,10 +11846,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2">
@@ -11710,10 +11871,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2">
@@ -11735,10 +11896,10 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2">
@@ -11760,10 +11921,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2">
@@ -11786,7 +11947,7 @@
     <row r="24" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="17" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="34">
@@ -11813,7 +11974,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="78" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B25" s="78"/>
       <c r="C25" s="78"/>
@@ -11826,10 +11987,10 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2">
@@ -11851,10 +12012,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2">
@@ -11876,10 +12037,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2">
@@ -11901,10 +12062,10 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2">
@@ -11926,10 +12087,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2">
@@ -11952,7 +12113,7 @@
     <row r="31" spans="1:9">
       <c r="A31" s="17"/>
       <c r="B31" s="17" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="34">
@@ -11979,7 +12140,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="78" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B32" s="78"/>
       <c r="C32" s="78"/>
@@ -11995,7 +12156,7 @@
         <v>313</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="2">
@@ -12020,7 +12181,7 @@
         <v>313</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2">
@@ -12043,7 +12204,7 @@
     <row r="35" spans="1:9">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="34">
@@ -12070,7 +12231,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="78" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B36" s="78"/>
       <c r="C36" s="78"/>
@@ -12086,7 +12247,7 @@
         <v>512</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2">
@@ -12111,7 +12272,7 @@
         <v>512</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2">
@@ -12136,7 +12297,7 @@
         <v>512</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="2">
@@ -12161,7 +12322,7 @@
         <v>512</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="2">
@@ -12186,7 +12347,7 @@
         <v>512</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="2">
@@ -12209,7 +12370,7 @@
     <row r="42" spans="1:9">
       <c r="A42" s="17"/>
       <c r="B42" s="17" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="34">
@@ -12236,7 +12397,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="78" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B43" s="78"/>
       <c r="C43" s="78"/>
@@ -12249,10 +12410,10 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2">
@@ -12274,10 +12435,10 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="2">
@@ -12299,10 +12460,10 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="2">
@@ -12324,10 +12485,10 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2">
@@ -12349,10 +12510,10 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="2">
@@ -12374,10 +12535,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="2">
@@ -12399,10 +12560,10 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="2">
@@ -12425,7 +12586,7 @@
     <row r="51" spans="1:9">
       <c r="A51" s="17"/>
       <c r="B51" s="17" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="34">
@@ -12453,28 +12614,28 @@
     <row r="53" spans="1:9">
       <c r="A53" s="35"/>
       <c r="B53" s="35" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C53" s="36"/>
       <c r="D53" s="37">
         <f>D4+D11+D14+D24+D31+D35+D42+D51</f>
-        <v>1791995</v>
+        <v>1837139</v>
       </c>
       <c r="E53" s="37">
         <f>E4+E11+E14+E24+E31+E35+E42+E51</f>
-        <v>3295700.6</v>
+        <v>3365468.6</v>
       </c>
       <c r="F53" s="37">
         <f>F4+F11+F14+F24+F31+F35+F42+F51</f>
-        <v>3964451.8000000003</v>
+        <v>4046531.8000000003</v>
       </c>
       <c r="G53" s="37">
         <f>G4+G11+G14+G24+G31+G35+G42+G51</f>
-        <v>4015920</v>
+        <v>4098000</v>
       </c>
       <c r="H53" s="37">
         <f>H4+H11+H14+H24+H31+H35+H42+H51</f>
-        <v>4035920</v>
+        <v>4118000</v>
       </c>
       <c r="I53" s="36"/>
     </row>
@@ -12524,22 +12685,22 @@
         <v>308</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>101</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>72</v>
@@ -12547,7 +12708,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="78" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -12561,13 +12722,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D3" s="1">
         <v>5</v>
@@ -12587,18 +12748,18 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D4" s="1">
         <v>22</v>
@@ -12621,13 +12782,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D5" s="1">
         <v>30</v>
@@ -12650,13 +12811,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
@@ -12679,13 +12840,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D7" s="1">
         <v>55</v>
@@ -12705,18 +12866,18 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12739,13 +12900,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -12768,13 +12929,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D10" s="1">
         <v>22</v>
@@ -12797,13 +12958,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D11" s="1">
         <v>18</v>
@@ -12826,13 +12987,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D12" s="1">
         <v>15</v>
@@ -12852,18 +13013,18 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -12886,13 +13047,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D14" s="1">
         <v>22</v>
@@ -12915,13 +13076,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D15" s="1">
         <v>30</v>
@@ -12944,13 +13105,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D16" s="1">
         <v>22</v>
@@ -12973,13 +13134,13 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D17" s="1">
         <v>37</v>
@@ -13005,10 +13166,10 @@
         <v>281</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D18" s="1">
         <v>15</v>
@@ -13028,7 +13189,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -13036,10 +13197,10 @@
         <v>281</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D19" s="1">
         <v>7</v>
@@ -13065,10 +13226,10 @@
         <v>281</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D20" s="1">
         <v>30</v>
@@ -13088,7 +13249,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -13096,10 +13257,10 @@
         <v>281</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D21" s="1">
         <v>0.75</v>
@@ -13119,13 +13280,13 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="17"/>
       <c r="B22" s="17" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -13148,7 +13309,7 @@
     <row r="23" spans="1:10">
       <c r="A23" s="44"/>
       <c r="B23" s="44" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="45"/>
@@ -13161,13 +13322,13 @@
       </c>
       <c r="I23" s="45"/>
       <c r="J23" s="45" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="35"/>
       <c r="B24" s="35" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
@@ -13182,9 +13343,9 @@
       <c r="J24" s="36"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73" t="s">
-        <v>659</v>
+      <c r="A25" s="75"/>
+      <c r="B25" s="75" t="s">
+        <v>662</v>
       </c>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
@@ -13197,12 +13358,12 @@
         <v>318780</v>
       </c>
       <c r="J25" s="63" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="78" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B27" s="78"/>
       <c r="C27" s="78"/>
@@ -13217,7 +13378,7 @@
     <row r="28" spans="1:10">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -13233,16 +13394,16 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E29" s="32">
         <v>50</v>
@@ -13261,16 +13422,16 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E30" s="32">
         <v>30</v>
@@ -13289,14 +13450,14 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E31" s="32">
         <v>10</v>
@@ -13318,13 +13479,13 @@
         <v>281</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E32" s="32">
         <v>20</v>
@@ -13346,11 +13507,11 @@
         <v>281</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E33" s="32">
         <v>10</v>
@@ -13372,13 +13533,13 @@
         <v>281</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>382</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E34" s="32">
         <v>24</v>
@@ -13398,7 +13559,7 @@
     <row r="35" spans="1:10">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
@@ -13421,7 +13582,7 @@
     <row r="36" spans="1:10">
       <c r="A36" s="44"/>
       <c r="B36" s="44" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
@@ -13438,7 +13599,7 @@
     <row r="37" spans="1:10">
       <c r="A37" s="57"/>
       <c r="B37" s="57" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
@@ -13454,7 +13615,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="79" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B39" s="80"/>
       <c r="C39" s="80"/>
@@ -13502,16 +13663,16 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E43" s="32">
         <v>5</v>
@@ -13532,7 +13693,7 @@
         <v>15600</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -13540,13 +13701,13 @@
         <v>481</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E44" s="32">
         <v>1</v>
@@ -13573,13 +13734,13 @@
         <v>481</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E45" s="32">
         <v>1</v>
@@ -13600,7 +13761,7 @@
         <v>2340</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -13608,13 +13769,13 @@
         <v>481</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E46" s="32">
         <v>1</v>
@@ -13635,7 +13796,7 @@
         <v>1872</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -13643,13 +13804,13 @@
         <v>481</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E47" s="32">
         <v>1</v>
@@ -13670,21 +13831,21 @@
         <v>2808</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
@@ -13705,21 +13866,21 @@
         <v>4680</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -13727,13 +13888,13 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="17"/>
       <c r="B50" s="17" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
@@ -13749,12 +13910,12 @@
         <v>29640</v>
       </c>
       <c r="J50" s="19" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="82" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B52" s="82"/>
       <c r="C52" s="82"/>
@@ -13769,7 +13930,7 @@
     <row r="53" spans="1:10">
       <c r="A53" s="9"/>
       <c r="B53" s="9" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
@@ -13786,7 +13947,7 @@
     <row r="54" spans="1:10">
       <c r="A54" s="9"/>
       <c r="B54" s="9" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -13803,7 +13964,7 @@
     <row r="55" spans="1:10">
       <c r="A55" s="9"/>
       <c r="B55" s="9" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
@@ -13820,7 +13981,7 @@
     <row r="56" spans="1:10">
       <c r="A56" s="57"/>
       <c r="B56" s="57" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C56" s="58"/>
       <c r="D56" s="58"/>
@@ -13868,7 +14029,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="26" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="28"/>
@@ -13880,16 +14041,16 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B2" s="47">
         <f>OPEX_Operations!F53/12</f>
-        <v>330370.98333333334</v>
+        <v>337210.98333333334</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B3" s="47">
         <f>(Assumptions!B40+Assumptions!B41+Assumptions!B42)/12</f>
@@ -13898,39 +14059,39 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B4" s="48">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.85">
       <c r="A6" s="15" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -13938,14 +14099,14 @@
         <v>321</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
       </c>
       <c r="D7" s="2">
         <f>$B$2*MAX(C7,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E7" s="2">
         <f>$B$3*C7</f>
@@ -13953,14 +14114,14 @@
       </c>
       <c r="F7" s="2">
         <f>E7-D7</f>
-        <v>-46251.937666666672</v>
+        <v>-47209.537666666671</v>
       </c>
       <c r="G7" s="2">
         <f>F7</f>
-        <v>-46251.937666666672</v>
+        <v>-47209.537666666671</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -13968,14 +14129,14 @@
         <v>502</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
       </c>
       <c r="D8" s="2">
         <f>$B$2*MAX(C8,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E8" s="2">
         <f>$B$3*C8</f>
@@ -13983,14 +14144,14 @@
       </c>
       <c r="F8" s="2">
         <f>E8-D8</f>
-        <v>-46251.937666666672</v>
+        <v>-47209.537666666671</v>
       </c>
       <c r="G8" s="2">
         <f>G7+F8</f>
-        <v>-92503.875333333344</v>
+        <v>-94419.075333333341</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -13998,14 +14159,14 @@
         <v>370</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C9" s="16">
         <v>0.05</v>
       </c>
       <c r="D9" s="2">
         <f>$B$2*MAX(C9,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E9" s="2">
         <f>$B$3*C9</f>
@@ -14013,14 +14174,14 @@
       </c>
       <c r="F9" s="2">
         <f>E9-D9</f>
-        <v>3748.0623333333278</v>
+        <v>2790.4623333333293</v>
       </c>
       <c r="G9" s="2">
         <f>G8+F9</f>
-        <v>-88755.813000000024</v>
+        <v>-91628.613000000012</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -14028,14 +14189,14 @@
         <v>426</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C10" s="16">
         <v>0.08</v>
       </c>
       <c r="D10" s="2">
         <f>$B$2*MAX(C10,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E10" s="2">
         <f>$B$3*C10</f>
@@ -14043,14 +14204,14 @@
       </c>
       <c r="F10" s="2">
         <f>E10-D10</f>
-        <v>33748.062333333328</v>
+        <v>32790.462333333329</v>
       </c>
       <c r="G10" s="2">
         <f>G9+F10</f>
-        <v>-55007.750666666696</v>
+        <v>-58838.150666666683</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -14058,14 +14219,14 @@
         <v>514</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C11" s="16">
         <v>0.1</v>
       </c>
       <c r="D11" s="2">
         <f>$B$2*MAX(C11,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E11" s="2">
         <f>$B$3*C11</f>
@@ -14073,14 +14234,14 @@
       </c>
       <c r="F11" s="2">
         <f>E11-D11</f>
-        <v>53748.062333333328</v>
+        <v>52790.462333333329</v>
       </c>
       <c r="G11" s="2">
         <f>G10+F11</f>
-        <v>-1259.6883333333681</v>
+        <v>-6047.6883333333535</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -14088,14 +14249,14 @@
         <v>504</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C12" s="16">
         <v>0.12</v>
       </c>
       <c r="D12" s="2">
         <f>$B$2*MAX(C12,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E12" s="2">
         <f>$B$3*C12</f>
@@ -14103,29 +14264,29 @@
       </c>
       <c r="F12" s="2">
         <f>E12-D12</f>
-        <v>73748.062333333335</v>
+        <v>72790.462333333329</v>
       </c>
       <c r="G12" s="2">
         <f>G11+F12</f>
-        <v>72488.373999999967</v>
+        <v>66742.773999999976</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C13" s="16">
         <v>0.12</v>
       </c>
       <c r="D13" s="2">
         <f>$B$2*MAX(C13,$B$4)</f>
-        <v>46251.937666666672</v>
+        <v>47209.537666666671</v>
       </c>
       <c r="E13" s="2">
         <f>$B$3*C13</f>
@@ -14133,14 +14294,14 @@
       </c>
       <c r="F13" s="2">
         <f>E13-D13</f>
-        <v>73748.062333333335</v>
+        <v>72790.462333333329</v>
       </c>
       <c r="G13" s="2">
         <f>G12+F13</f>
-        <v>146236.43633333332</v>
+        <v>139533.23633333331</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14148,14 +14309,14 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C14" s="16">
         <v>0.15</v>
       </c>
       <c r="D14" s="2">
         <f>$B$2*MAX(C14,$B$4)</f>
-        <v>49555.647499999999</v>
+        <v>50581.647499999999</v>
       </c>
       <c r="E14" s="2">
         <f>$B$3*C14</f>
@@ -14163,29 +14324,29 @@
       </c>
       <c r="F14" s="2">
         <f>E14-D14</f>
-        <v>100444.35250000001</v>
+        <v>99418.352500000008</v>
       </c>
       <c r="G14" s="2">
         <f>G13+F14</f>
-        <v>246680.78883333332</v>
+        <v>238951.58883333331</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C15" s="16">
         <v>0.25</v>
       </c>
       <c r="D15" s="2">
         <f>$B$2*MAX(C15,$B$4)</f>
-        <v>82592.745833333334</v>
+        <v>84302.745833333334</v>
       </c>
       <c r="E15" s="2">
         <f>$B$3*C15</f>
@@ -14193,14 +14354,14 @@
       </c>
       <c r="F15" s="2">
         <f>E15-D15</f>
-        <v>167407.25416666665</v>
+        <v>165697.25416666665</v>
       </c>
       <c r="G15" s="2">
         <f>G14+F15</f>
-        <v>414088.04299999995</v>
+        <v>404648.84299999999</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -14208,14 +14369,14 @@
         <v>428</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C16" s="16">
         <v>0.35</v>
       </c>
       <c r="D16" s="2">
         <f>$B$2*MAX(C16,$B$4)</f>
-        <v>115629.84416666666</v>
+        <v>118023.84416666666</v>
       </c>
       <c r="E16" s="2">
         <f>$B$3*C16</f>
@@ -14223,29 +14384,29 @@
       </c>
       <c r="F16" s="2">
         <f>E16-D16</f>
-        <v>234370.15583333332</v>
+        <v>231976.15583333332</v>
       </c>
       <c r="G16" s="2">
         <f>G15+F16</f>
-        <v>648458.19883333333</v>
+        <v>636624.99883333337</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C17" s="16">
         <v>0.42</v>
       </c>
       <c r="D17" s="2">
         <f>$B$2*MAX(C17,$B$4)</f>
-        <v>138755.81299999999</v>
+        <v>141628.61299999998</v>
       </c>
       <c r="E17" s="2">
         <f>$B$3*C17</f>
@@ -14253,14 +14414,14 @@
       </c>
       <c r="F17" s="2">
         <f>E17-D17</f>
-        <v>281244.18700000003</v>
+        <v>278371.38699999999</v>
       </c>
       <c r="G17" s="2">
         <f>G16+F17</f>
-        <v>929702.38583333336</v>
+        <v>914996.38583333336</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -14268,14 +14429,14 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C18" s="16">
         <v>0.48</v>
       </c>
       <c r="D18" s="2">
         <f>$B$2*MAX(C18,$B$4)</f>
-        <v>158578.07199999999</v>
+        <v>161861.272</v>
       </c>
       <c r="E18" s="2">
         <f>$B$3*C18</f>
@@ -14283,29 +14444,29 @@
       </c>
       <c r="F18" s="2">
         <f>E18-D18</f>
-        <v>321421.92800000001</v>
+        <v>318138.728</v>
       </c>
       <c r="G18" s="2">
         <f>G17+F18</f>
-        <v>1251124.3138333333</v>
+        <v>1233135.1138333334</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C19" s="16">
         <v>0.52</v>
       </c>
       <c r="D19" s="2">
         <f>$B$2*MAX(C19,$B$4)</f>
-        <v>171792.91133333335</v>
+        <v>175349.71133333334</v>
       </c>
       <c r="E19" s="2">
         <f>$B$3*C19</f>
@@ -14313,29 +14474,29 @@
       </c>
       <c r="F19" s="2">
         <f>E19-D19</f>
-        <v>348207.08866666665</v>
+        <v>344650.28866666666</v>
       </c>
       <c r="G19" s="2">
         <f>G18+F19</f>
-        <v>1599331.4024999999</v>
+        <v>1577785.4025000001</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C20" s="16">
         <v>0.55000000000000004</v>
       </c>
       <c r="D20" s="2">
         <f>$B$2*MAX(C20,$B$4)</f>
-        <v>181704.04083333336</v>
+        <v>185466.04083333336</v>
       </c>
       <c r="E20" s="2">
         <f>$B$3*C20</f>
@@ -14343,29 +14504,29 @@
       </c>
       <c r="F20" s="2">
         <f>E20-D20</f>
-        <v>368295.95916666661</v>
+        <v>364533.95916666661</v>
       </c>
       <c r="G20" s="2">
         <f>G19+F20</f>
-        <v>1967627.3616666663</v>
+        <v>1942319.3616666668</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C21" s="16">
         <v>0.57999999999999996</v>
       </c>
       <c r="D21" s="2">
         <f>$B$2*MAX(C21,$B$4)</f>
-        <v>191615.17033333331</v>
+        <v>195582.37033333333</v>
       </c>
       <c r="E21" s="2">
         <f>$B$3*C21</f>
@@ -14373,29 +14534,29 @@
       </c>
       <c r="F21" s="2">
         <f>E21-D21</f>
-        <v>388384.82966666669</v>
+        <v>384417.62966666667</v>
       </c>
       <c r="G21" s="2">
         <f>G20+F21</f>
-        <v>2356012.191333333</v>
+        <v>2326736.9913333333</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C22" s="16">
         <v>0.62</v>
       </c>
       <c r="D22" s="2">
         <f>$B$2*MAX(C22,$B$4)</f>
-        <v>204830.00966666668</v>
+        <v>209070.80966666667</v>
       </c>
       <c r="E22" s="2">
         <f>$B$3*C22</f>
@@ -14403,29 +14564,29 @@
       </c>
       <c r="F22" s="2">
         <f>E22-D22</f>
-        <v>415169.99033333332</v>
+        <v>410929.19033333333</v>
       </c>
       <c r="G22" s="2">
         <f>G21+F22</f>
-        <v>2771182.1816666662</v>
+        <v>2737666.1816666666</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C23" s="16">
         <v>0.66</v>
       </c>
       <c r="D23" s="2">
         <f>$B$2*MAX(C23,$B$4)</f>
-        <v>218044.84900000002</v>
+        <v>222559.24900000001</v>
       </c>
       <c r="E23" s="2">
         <f>$B$3*C23</f>
@@ -14433,29 +14594,29 @@
       </c>
       <c r="F23" s="2">
         <f>E23-D23</f>
-        <v>441955.15099999995</v>
+        <v>437440.75099999999</v>
       </c>
       <c r="G23" s="2">
         <f>G22+F23</f>
-        <v>3213137.3326666662</v>
+        <v>3175106.9326666668</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C24" s="16">
         <v>0.7</v>
       </c>
       <c r="D24" s="2">
         <f>$B$2*MAX(C24,$B$4)</f>
-        <v>231259.68833333332</v>
+        <v>236047.68833333332</v>
       </c>
       <c r="E24" s="2">
         <f>$B$3*C24</f>
@@ -14463,29 +14624,29 @@
       </c>
       <c r="F24" s="2">
         <f>E24-D24</f>
-        <v>468740.31166666665</v>
+        <v>463952.31166666665</v>
       </c>
       <c r="G24" s="2">
         <f>G23+F24</f>
-        <v>3681877.6443333328</v>
+        <v>3639059.2443333333</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C25" s="16">
         <v>0.74</v>
       </c>
       <c r="D25" s="2">
         <f>$B$2*MAX(C25,$B$4)</f>
-        <v>244474.52766666666</v>
+        <v>249536.12766666667</v>
       </c>
       <c r="E25" s="2">
         <f>$B$3*C25</f>
@@ -14493,29 +14654,29 @@
       </c>
       <c r="F25" s="2">
         <f>E25-D25</f>
-        <v>495525.47233333334</v>
+        <v>490463.87233333336</v>
       </c>
       <c r="G25" s="2">
         <f>G24+F25</f>
-        <v>4177403.1166666662</v>
+        <v>4129523.1166666667</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C26" s="16">
         <v>0.78</v>
       </c>
       <c r="D26" s="2">
         <f>$B$2*MAX(C26,$B$4)</f>
-        <v>257689.367</v>
+        <v>263024.56700000004</v>
       </c>
       <c r="E26" s="2">
         <f>$B$3*C26</f>
@@ -14523,29 +14684,29 @@
       </c>
       <c r="F26" s="2">
         <f>E26-D26</f>
-        <v>522310.63300000003</v>
+        <v>516975.43299999996</v>
       </c>
       <c r="G26" s="2">
         <f>G25+F26</f>
-        <v>4699713.7496666666</v>
+        <v>4646498.5496666664</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C27" s="16">
         <v>0.82</v>
       </c>
       <c r="D27" s="2">
         <f>$B$2*MAX(C27,$B$4)</f>
-        <v>270904.20633333334</v>
+        <v>276513.00633333332</v>
       </c>
       <c r="E27" s="2">
         <f>$B$3*C27</f>
@@ -14553,29 +14714,29 @@
       </c>
       <c r="F27" s="2">
         <f>E27-D27</f>
-        <v>549095.79366666661</v>
+        <v>543486.99366666668</v>
       </c>
       <c r="G27" s="2">
         <f>G26+F27</f>
-        <v>5248809.543333333</v>
+        <v>5189985.543333333</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C28" s="16">
         <v>0.86</v>
       </c>
       <c r="D28" s="2">
         <f>$B$2*MAX(C28,$B$4)</f>
-        <v>284119.04566666664</v>
+        <v>290001.44566666667</v>
       </c>
       <c r="E28" s="2">
         <f>$B$3*C28</f>
@@ -14583,29 +14744,29 @@
       </c>
       <c r="F28" s="2">
         <f>E28-D28</f>
-        <v>575880.9543333333</v>
+        <v>569998.55433333339</v>
       </c>
       <c r="G28" s="2">
         <f>G27+F28</f>
-        <v>5824690.4976666663</v>
+        <v>5759984.0976666659</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C29" s="16">
         <v>0.9</v>
       </c>
       <c r="D29" s="2">
         <f>$B$2*MAX(C29,$B$4)</f>
-        <v>297333.88500000001</v>
+        <v>303489.88500000001</v>
       </c>
       <c r="E29" s="2">
         <f>$B$3*C29</f>
@@ -14613,14 +14774,14 @@
       </c>
       <c r="F29" s="2">
         <f>E29-D29</f>
-        <v>602666.11499999999</v>
+        <v>596510.11499999999</v>
       </c>
       <c r="G29" s="2">
         <f>G28+F29</f>
-        <v>6427356.6126666665</v>
+        <v>6356494.2126666661</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -14628,14 +14789,14 @@
         <v>452</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C30" s="16">
         <v>0.95</v>
       </c>
       <c r="D30" s="2">
         <f>$B$2*MAX(C30,$B$4)</f>
-        <v>313852.43416666664</v>
+        <v>320350.43416666664</v>
       </c>
       <c r="E30" s="2">
         <f>$B$3*C30</f>
@@ -14643,19 +14804,19 @@
       </c>
       <c r="F30" s="2">
         <f>E30-D30</f>
-        <v>636147.56583333341</v>
+        <v>629649.56583333341</v>
       </c>
       <c r="G30" s="2">
         <f>G29+F30</f>
-        <v>7063504.1785000004</v>
+        <v>6986143.7785</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="78" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B32" s="78"/>
       <c r="C32" s="78"/>
@@ -14665,19 +14826,19 @@
       <c r="G32" s="78"/>
       <c r="H32" s="78"/>
       <c r="J32" s="72" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="K32" s="72" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="L32" s="72" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="35"/>
       <c r="B33" s="35" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -14685,23 +14846,23 @@
       <c r="F33" s="36"/>
       <c r="G33" s="37">
         <f>MIN(G7:G30)</f>
-        <v>-92503.875333333344</v>
+        <v>-94419.075333333341</v>
       </c>
       <c r="H33" s="36"/>
       <c r="J33" s="67" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="K33" s="68" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="L33" s="68" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="35"/>
       <c r="B34" s="35" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C34" s="36"/>
       <c r="D34" s="36"/>
@@ -14712,22 +14873,22 @@
         <v>25</v>
       </c>
       <c r="H34" s="36" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="J34" s="67" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="K34" s="68" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="L34" s="68" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="26"/>
       <c r="B35" s="26" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
@@ -14735,23 +14896,23 @@
       <c r="F35" s="28"/>
       <c r="G35" s="50">
         <f>ABS(G33)*G34</f>
-        <v>2312596.8833333338</v>
+        <v>2360476.8833333338</v>
       </c>
       <c r="H35" s="28"/>
       <c r="J35" s="67" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="K35" s="67" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="L35" s="68" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="51"/>
       <c r="B36" s="51" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C36" s="52"/>
       <c r="D36" s="52"/>
@@ -14759,25 +14920,25 @@
       <c r="F36" s="52"/>
       <c r="G36" s="53">
         <f>G35-ABS(G33)</f>
-        <v>2220093.0080000004</v>
+        <v>2266057.8080000002</v>
       </c>
       <c r="H36" s="52" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="J36" s="69" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="K36" s="70">
         <v>25</v>
       </c>
       <c r="L36" s="71" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="51"/>
       <c r="B37" s="51" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C37" s="52"/>
       <c r="D37" s="52"/>
@@ -14785,17 +14946,17 @@
       <c r="F37" s="52"/>
       <c r="G37" s="54">
         <f>IF(G33=0,0,G35/ABS(G33)-1)</f>
-        <v>24</v>
+        <v>24.000000000000004</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I37" s="66"/>
     </row>
     <row r="39" spans="1:12" ht="22.35" customHeight="1">
-      <c r="A39" s="73"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="83" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C39" s="83"/>
       <c r="D39" s="83"/>

--- a/docs/EN/EN_TakaPlast_Budget.xlsx
+++ b/docs/EN/EN_TakaPlast_Budget.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="505" documentId="11_6A32D4F240207C91FB7A9A1550F542CAE46E6FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81777FA6-0CBC-449A-8D93-AFF8835B1641}"/>
+  <xr:revisionPtr revIDLastSave="530" documentId="11_6A32D4F240207C91FB7A9A1550F542CAE46E6FA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7603C06-7F7F-40EC-85F3-38E6E4EA57F1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="927">
   <si>
     <t>TAKAPLAST — SUMMARY</t>
   </si>
@@ -1450,6 +1450,12 @@
     <t>Process expert</t>
   </si>
   <si>
+    <t>M0-M8</t>
+  </si>
+  <si>
+    <t>Technical Installation Consultant – 3-Flow Process Expert (12–18 month assignment)</t>
+  </si>
+  <si>
     <t>Subtotal TRAINING</t>
   </si>
   <si>
@@ -1486,6 +1492,9 @@
     <t>Start</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>EXECUTIVE TEAM</t>
   </si>
   <si>
@@ -1501,36 +1510,54 @@
     <t>M0 — strategic vision, investors, expansion</t>
   </si>
   <si>
+    <t>www.linkedin.com/in/joeloxybel</t>
+  </si>
+  <si>
     <t>Managing Director / Gérant statutaire</t>
   </si>
   <si>
     <t>M12 — daily operations, legal representative</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/patrick-kahasha-mbasha-1a177323/</t>
+  </si>
+  <si>
     <t>Chief Technology Officer (CTO)</t>
   </si>
   <si>
     <t>M1 — critical, plant engineering</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/jiry-ngoma-b4872a143/</t>
+  </si>
+  <si>
     <t>Chief Operating Officer (COO)</t>
   </si>
   <si>
     <t>M1 — supply chain, logistics</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/serge-tshishimbi-2b3396140/</t>
+  </si>
+  <si>
     <t>Chief Commercial Officer (CCO)</t>
   </si>
   <si>
     <t>M8 — sales 3 flux + export</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/serge-bazola-ndelo-59551941/</t>
+  </si>
+  <si>
     <t>Chief Marketing Officer (CMO)</t>
   </si>
   <si>
     <t>M4 — brand, positioning, market penetration</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/aurorejoncour/</t>
+  </si>
+  <si>
     <t>Chief Financial Officer (CFO)</t>
   </si>
   <si>
@@ -1603,13 +1630,25 @@
     <t>B2B Sales Industry / Energy</t>
   </si>
   <si>
-    <t>B2B Sales BPT</t>
+    <t>https://www.linkedin.com/in/etienne-titi-bakadisansa-62136340/</t>
+  </si>
+  <si>
+    <t>B2B Sales BTP</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/augustin-mbongu-1a3384235/</t>
   </si>
   <si>
     <t>B2B Sales Distribution / Resellers</t>
   </si>
   <si>
-    <t>Sales Multipurpose Land</t>
+    <t>https://www.linkedin.com/in/choudhary-muhammad-aamir-saeed-8b45a250/</t>
+  </si>
+  <si>
+    <t>Multipurpose land / key accounts</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sarahmukonga91/</t>
   </si>
   <si>
     <t>OPERATIONS</t>
@@ -2798,7 +2837,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2884,6 +2923,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -3074,10 +3121,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3263,9 +3311,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3278,10 +3329,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4119,18 +4173,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
@@ -4138,7 +4192,7 @@
       </c>
       <c r="B4" s="2">
         <f>CAPEX_Consolidated!B17</f>
-        <v>6125369.5999999996</v>
+        <v>6179129.5999999996</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -4160,18 +4214,18 @@
       </c>
       <c r="B6" s="5">
         <f>CAPEX_Consolidated!B20</f>
-        <v>8485846.4833333343</v>
+        <v>8539606.4833333343</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
@@ -4249,11 +4303,11 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
@@ -4429,11 +4483,11 @@
       <c r="C35" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="76" t="s">
+      <c r="A37" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="76"/>
-      <c r="C37" s="76"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
@@ -4541,11 +4595,11 @@
       <c r="C48" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="76" t="s">
+      <c r="A51" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="76"/>
-      <c r="C51" s="76"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="79"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="7" t="s">
@@ -4610,43 +4664,43 @@
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75">
-      <c r="A84" s="76" t="s">
+      <c r="A84" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="76"/>
-      <c r="C84" s="76"/>
+      <c r="B84" s="79"/>
+      <c r="C84" s="79"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="77" t="s">
+      <c r="A85" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B85" s="77"/>
-      <c r="C85" s="77"/>
+      <c r="B85" s="80"/>
+      <c r="C85" s="80"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="77"/>
+      <c r="A86" s="80"/>
+      <c r="B86" s="80"/>
+      <c r="C86" s="80"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="77"/>
+      <c r="A87" s="80"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="80"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="77"/>
+      <c r="A88" s="80"/>
+      <c r="B88" s="80"/>
+      <c r="C88" s="80"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="77"/>
+      <c r="A89" s="80"/>
+      <c r="B89" s="80"/>
+      <c r="C89" s="80"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="77"/>
+      <c r="A90" s="80"/>
+      <c r="B90" s="80"/>
+      <c r="C90" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4689,47 +4743,47 @@
         <v>59</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>793</v>
+        <v>806</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="78" t="s">
-        <v>796</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="81" t="s">
+        <v>809</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
@@ -4739,10 +4793,10 @@
         <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="E3" s="2">
         <f>Assumptions!B40*Assumptions!B30</f>
@@ -4768,7 +4822,7 @@
         <v>0.48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4776,13 +4830,13 @@
         <v>263</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>800</v>
+        <v>813</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
       <c r="E4" s="2">
         <f>Assumptions!B41*Assumptions!B30</f>
@@ -4808,7 +4862,7 @@
         <v>0.45</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4816,13 +4870,13 @@
         <v>239</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>805</v>
+        <v>818</v>
       </c>
       <c r="E5" s="2">
         <f>Assumptions!B42*Assumptions!B30</f>
@@ -4848,13 +4902,13 @@
         <v>0.52</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="17"/>
       <c r="B6" s="17" t="s">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -4882,27 +4936,27 @@
       <c r="K6" s="19"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="78" t="s">
-        <v>807</v>
-      </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="78"/>
+      <c r="A8" s="81" t="s">
+        <v>820</v>
+      </c>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>808</v>
+        <v>821</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>809</v>
+        <v>822</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2">
@@ -4927,16 +4981,16 @@
         <v>86</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>810</v>
+        <v>823</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>811</v>
+        <v>824</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="2">
@@ -4962,16 +5016,16 @@
         <v>45</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>813</v>
+        <v>826</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>814</v>
+        <v>827</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>815</v>
+        <v>828</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2">
@@ -4995,13 +5049,13 @@
         <v>38</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>816</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>169</v>
@@ -5028,16 +5082,16 @@
         <v>65</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>818</v>
+        <v>831</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>819</v>
+        <v>832</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2">
@@ -5060,13 +5114,13 @@
         <v>75</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>822</v>
+        <v>835</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -5096,7 +5150,7 @@
     <row r="16" spans="1:11">
       <c r="A16" s="35"/>
       <c r="B16" s="35" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
@@ -5124,24 +5178,24 @@
       <c r="K16" s="36"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="78" t="s">
-        <v>824</v>
-      </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
+      <c r="A18" s="81" t="s">
+        <v>837</v>
+      </c>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="9"/>
       <c r="B19" s="9" t="s">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -5171,7 +5225,7 @@
     <row r="20" spans="1:11">
       <c r="A20" s="9"/>
       <c r="B20" s="9" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -5201,7 +5255,7 @@
     <row r="21" spans="1:11">
       <c r="A21" s="35"/>
       <c r="B21" s="35" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
@@ -5231,7 +5285,7 @@
     <row r="22" spans="1:11">
       <c r="A22" s="44"/>
       <c r="B22" s="44" t="s">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="45"/>
@@ -5288,228 +5342,228 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
-        <v>829</v>
+        <v>842</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>830</v>
+        <v>843</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>831</v>
+        <v>844</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>832</v>
+        <v>845</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>834</v>
+        <v>847</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>835</v>
+        <v>848</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>836</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="78" t="s">
-        <v>837</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="81" t="s">
+        <v>850</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="9" t="s">
-        <v>838</v>
+        <v>851</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>839</v>
+        <v>852</v>
       </c>
       <c r="C3" s="43">
         <v>600000</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="9" t="s">
-        <v>845</v>
+        <v>858</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="C4" s="43">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>848</v>
+        <v>861</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>851</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="9" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>853</v>
+        <v>866</v>
       </c>
       <c r="C5" s="43">
         <v>500000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>855</v>
+        <v>868</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="9" t="s">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="C6" s="43">
         <v>150000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="9" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="C7" s="43">
         <v>500000</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>867</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="9" t="s">
-        <v>868</v>
+        <v>881</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="C8" s="43">
         <v>500000</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="9" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="C9" s="43">
         <v>300000</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="C10" s="34">
         <v>2800000</v>
@@ -5521,125 +5575,125 @@
       <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="78" t="s">
-        <v>879</v>
-      </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="A11" s="81" t="s">
+        <v>892</v>
+      </c>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="9" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>881</v>
+        <v>894</v>
       </c>
       <c r="C12" s="43">
         <v>500000</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="9" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="C13" s="43">
         <v>200000</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>855</v>
+        <v>868</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="C14" s="43">
         <v>300000</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>891</v>
+        <v>904</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="9" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>894</v>
+        <v>907</v>
       </c>
       <c r="C15" s="43">
         <v>1000000</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="17"/>
       <c r="B16" s="17" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="C16" s="34">
         <v>2000000</v>
@@ -5651,99 +5705,99 @@
       <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="78" t="s">
-        <v>898</v>
-      </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="A17" s="81" t="s">
+        <v>911</v>
+      </c>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="9" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="C18" s="43">
         <v>200000</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="9" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="C19" s="43">
         <v>100000</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>892</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="9" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="C20" s="43">
         <v>50000</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>436</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="17"/>
       <c r="B21" s="17" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="C21" s="34">
         <v>350000</v>
@@ -5757,7 +5811,7 @@
     <row r="23" spans="1:8">
       <c r="A23" s="35"/>
       <c r="B23" s="35" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="C23" s="37">
         <f>C10+C16+C21</f>
@@ -5770,16 +5824,16 @@
       <c r="H23" s="36"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
-      <c r="A25" s="75"/>
-      <c r="B25" s="83" t="s">
-        <v>913</v>
-      </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="86" t="s">
+        <v>926</v>
+      </c>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5822,12 +5876,12 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9" t="s">
@@ -5885,12 +5939,12 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="9" t="s">
@@ -5935,12 +5989,12 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="9" t="s">
@@ -6012,12 +6066,12 @@
       <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="9" t="s">
@@ -6063,12 +6117,12 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
@@ -6163,12 +6217,12 @@
       <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="78" t="s">
+      <c r="A29" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
@@ -6241,12 +6295,12 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="9" t="s">
@@ -6291,12 +6345,12 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="78" t="s">
+      <c r="A39" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="9" t="s">
@@ -6341,12 +6395,12 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="78" t="s">
+      <c r="A43" s="81" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="9" t="s">
@@ -6450,12 +6504,12 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="78" t="s">
+      <c r="A51" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="B51" s="78"/>
-      <c r="C51" s="78"/>
-      <c r="D51" s="78"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
     </row>
     <row r="52" spans="1:4" ht="24">
       <c r="A52" s="9" t="s">
@@ -6473,16 +6527,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6531,7 +6585,7 @@
       </c>
       <c r="C2" s="16">
         <f>B2/B17</f>
-        <v>0.34603626204041632</v>
+        <v>0.34302565850051114</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>179</v>
@@ -6550,7 +6604,7 @@
       </c>
       <c r="C3" s="16">
         <f>B3/B17</f>
-        <v>3.5589689151165671E-2</v>
+        <v>3.5280049798599465E-2</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>182</v>
@@ -6567,7 +6621,7 @@
       </c>
       <c r="C4" s="16">
         <f>B4/B17</f>
-        <v>9.3055609248460708E-2</v>
+        <v>9.2246001766980265E-2</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>182</v>
@@ -6584,7 +6638,7 @@
       </c>
       <c r="C5" s="16">
         <f>B5/B17</f>
-        <v>4.4895250076011743E-2</v>
+        <v>4.4504649975297496E-2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>182</v>
@@ -6601,7 +6655,7 @@
       </c>
       <c r="C6" s="16">
         <f>B6/B17</f>
-        <v>1.1917648201995845E-2</v>
+        <v>1.1813961629806243E-2</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>182</v>
@@ -6618,7 +6672,7 @@
       </c>
       <c r="C7" s="16">
         <f>B7/B17</f>
-        <v>4.4078972801902434E-3</v>
+        <v>4.3695474521201179E-3</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>182</v>
@@ -6635,7 +6689,7 @@
       </c>
       <c r="C8" s="16">
         <f>B8/B17</f>
-        <v>3.9181309157246607E-3</v>
+        <v>3.884042179662327E-3</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>182</v>
@@ -6652,7 +6706,7 @@
       </c>
       <c r="C9" s="16">
         <f>B9/B17</f>
-        <v>0.29141098685702166</v>
+        <v>0.28887563711238556</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>182</v>
@@ -6669,7 +6723,7 @@
       </c>
       <c r="C10" s="16">
         <f>B10/B17</f>
-        <v>1.8774377304514003E-2</v>
+        <v>1.8611035444215315E-2</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>182</v>
@@ -6686,7 +6740,7 @@
       </c>
       <c r="C11" s="16">
         <f>B11/B17</f>
-        <v>1.4856246388789341E-2</v>
+        <v>1.472699326455299E-2</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>182</v>
@@ -6699,11 +6753,11 @@
       </c>
       <c r="B12" s="2">
         <f>CAPEX_Infra_Vehicles_IT!F76</f>
-        <v>37000</v>
+        <v>85000</v>
       </c>
       <c r="C12" s="16">
         <f>B12/B17</f>
-        <v>6.0404518284088524E-3</v>
+        <v>1.3755982719637407E-2</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>182</v>
@@ -6720,7 +6774,7 @@
       </c>
       <c r="C13" s="16">
         <f>B13/B17</f>
-        <v>2.1954593564443851E-2</v>
+        <v>2.1763583013374572E-2</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>182</v>
@@ -6733,7 +6787,7 @@
       </c>
       <c r="B14" s="18">
         <f>SUM(B2:B13)</f>
-        <v>5469080</v>
+        <v>5517080</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -6745,7 +6799,7 @@
       </c>
       <c r="B15" s="21">
         <f>B14*Assumptions!B36</f>
-        <v>546908</v>
+        <v>551708</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22" t="s">
@@ -6761,7 +6815,7 @@
       </c>
       <c r="B16" s="21">
         <f>2%*B14</f>
-        <v>109381.6</v>
+        <v>110341.6</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
@@ -6775,7 +6829,7 @@
       </c>
       <c r="B17" s="24">
         <f>B14+B15+B16</f>
-        <v>6125369.5999999996</v>
+        <v>6179129.5999999996</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
@@ -6803,7 +6857,7 @@
       </c>
       <c r="B20" s="30">
         <f>B17+B19</f>
-        <v>8485846.4833333343</v>
+        <v>8539606.4833333343</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -6870,18 +6924,18 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
@@ -7148,18 +7202,18 @@
       <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
@@ -7418,18 +7472,18 @@
       <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="81" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
@@ -7686,18 +7740,18 @@
       <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="78" t="s">
+      <c r="A29" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
@@ -8087,7 +8141,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8117,16 +8171,16 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="81" t="s">
         <v>312</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
@@ -8219,16 +8273,16 @@
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="81" t="s">
         <v>323</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
@@ -8479,16 +8533,16 @@
       <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="81" t="s">
         <v>353</v>
       </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
@@ -8685,16 +8739,16 @@
       <c r="H26" s="19"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
@@ -8843,16 +8897,16 @@
       <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
@@ -8949,16 +9003,16 @@
       <c r="H38" s="19"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="78" t="s">
+      <c r="A39" s="81" t="s">
         <v>401</v>
       </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
@@ -9053,16 +9107,16 @@
       <c r="H43" s="19"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="81" t="s">
         <v>411</v>
       </c>
-      <c r="B44" s="78"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="78"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
@@ -9311,16 +9365,16 @@
       <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="78" t="s">
+      <c r="A55" s="81" t="s">
         <v>432</v>
       </c>
-      <c r="B55" s="78"/>
-      <c r="C55" s="78"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="78"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
@@ -9436,16 +9490,16 @@
       <c r="H60" s="19"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="81" t="s">
         <v>443</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="78"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
@@ -9672,16 +9726,16 @@
       <c r="H71" s="19"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="78" t="s">
+      <c r="A72" s="81" t="s">
         <v>458</v>
       </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="78"/>
-      <c r="H72" s="78"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
@@ -9747,28 +9801,30 @@
         <v>1</v>
       </c>
       <c r="E75" s="2">
-        <v>12000</v>
+        <v>60000</v>
       </c>
       <c r="F75" s="2">
         <f>D75*E75</f>
-        <v>12000</v>
+        <v>60000</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H75" s="1"/>
+        <v>468</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="17"/>
       <c r="B76" s="17" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="34">
         <f>SUM(F73:F75)</f>
-        <v>37000</v>
+        <v>85000</v>
       </c>
       <c r="G76" s="19"/>
       <c r="H76" s="19"/>
@@ -9776,30 +9832,30 @@
     <row r="78" spans="1:8" ht="26.85">
       <c r="A78" s="35"/>
       <c r="B78" s="35" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C78" s="36"/>
       <c r="D78" s="36"/>
       <c r="E78" s="36"/>
       <c r="F78" s="37">
         <f>F6+F17+F26+F33+F38+F43+F54+F60+F71+F76</f>
-        <v>3215000</v>
+        <v>3263000</v>
       </c>
       <c r="G78" s="36"/>
       <c r="H78" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9811,7 +9867,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -9823,64 +9879,69 @@
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="45.7109375" customWidth="1"/>
+    <col min="12" max="12" width="60.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="15" t="s">
         <v>306</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="78" t="s">
-        <v>480</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-    </row>
-    <row r="3" spans="1:11">
+        <v>481</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="81" t="s">
+        <v>483</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="75"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C3" s="39">
         <v>1</v>
@@ -9909,18 +9970,21 @@
         <v>336000</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K3" s="38" t="s">
+        <v>487</v>
+      </c>
+      <c r="L3" s="88" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="38" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="38" t="s">
-        <v>481</v>
-      </c>
       <c r="B4" s="38" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C4" s="39">
         <v>1</v>
@@ -9949,18 +10013,21 @@
         <v>134400</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>490</v>
+      </c>
+      <c r="L4" s="87" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C5" s="39">
         <v>1</v>
@@ -9989,18 +10056,21 @@
         <v>117600</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>493</v>
+      </c>
+      <c r="L5" s="87" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C6" s="39">
         <v>1</v>
@@ -10029,18 +10099,21 @@
         <v>108000</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>496</v>
+      </c>
+      <c r="L6" s="87" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C7" s="39">
         <v>1</v>
@@ -10069,18 +10142,21 @@
         <v>110400</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>499</v>
+      </c>
+      <c r="L7" s="87" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C8" s="39">
         <v>1</v>
@@ -10109,18 +10185,21 @@
         <v>67200</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>502</v>
+      </c>
+      <c r="L8" s="87" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="38" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C9" s="39">
         <v>1</v>
@@ -10149,16 +10228,17 @@
         <v>84000</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>505</v>
+      </c>
+      <c r="L9" s="38"/>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C10" s="41">
         <f>SUM(C3:C9)</f>
@@ -10175,28 +10255,30 @@
       </c>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="78" t="s">
-        <v>498</v>
-      </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="81" t="s">
+        <v>507</v>
+      </c>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="75"/>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="C12" s="39">
         <v>1</v>
@@ -10225,18 +10307,19 @@
         <v>58800</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>511</v>
+      </c>
+      <c r="L12" s="38"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C13" s="39">
         <v>1</v>
@@ -10265,18 +10348,19 @@
         <v>50400</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="L13" s="38"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C14" s="39">
         <v>1</v>
@@ -10305,18 +10389,19 @@
         <v>58800</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>511</v>
+      </c>
+      <c r="L14" s="38"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C15" s="39">
         <v>1</v>
@@ -10345,18 +10430,19 @@
         <v>50400</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K15" s="38" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" s="38"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C16" s="39">
         <v>1</v>
@@ -10385,18 +10471,19 @@
         <v>42000</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="L16" s="38"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="38" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C17" s="39">
         <v>1</v>
@@ -10425,16 +10512,17 @@
         <v>42000</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K17" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" s="38"/>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="17"/>
       <c r="B18" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C18" s="41">
         <f>SUM(C12:C17)</f>
@@ -10451,28 +10539,30 @@
       </c>
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="78" t="s">
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="81" t="s">
         <v>432</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="75"/>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="38" t="s">
         <v>433</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C20" s="39">
         <v>1</v>
@@ -10501,18 +10591,19 @@
         <v>58800</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K20" s="38" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" s="38"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="38" t="s">
         <v>433</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C21" s="39">
         <v>2</v>
@@ -10540,16 +10631,17 @@
         <v>62400</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K21" s="38" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" s="38"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="17"/>
       <c r="B22" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C22" s="41">
         <f>SUM(C20:C21)</f>
@@ -10566,28 +10658,30 @@
       </c>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="78" t="s">
-        <v>511</v>
-      </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L22" s="19"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="81" t="s">
+        <v>520</v>
+      </c>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="75"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="38" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C24" s="39">
         <v>1</v>
@@ -10615,18 +10709,19 @@
         <v>31200</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>523</v>
+      </c>
+      <c r="L24" s="38"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="38" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="C25" s="39">
         <v>1</v>
@@ -10654,16 +10749,17 @@
         <v>23400</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="L25" s="38"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="17"/>
       <c r="B26" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C26" s="41">
         <f>SUM(C24:C25)</f>
@@ -10680,28 +10776,30 @@
       </c>
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="78" t="s">
-        <v>516</v>
-      </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L26" s="19"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="81" t="s">
+        <v>525</v>
+      </c>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="75"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="38" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C28" s="39">
         <v>1</v>
@@ -10709,19 +10807,19 @@
       <c r="D28" s="40">
         <v>2000</v>
       </c>
-      <c r="E28" s="84">
+      <c r="E28" s="77">
         <f>C28*D28*12</f>
         <v>24000</v>
       </c>
-      <c r="F28" s="84">
+      <c r="F28" s="77">
         <f>E28*Assumptions!B37</f>
         <v>6000</v>
       </c>
-      <c r="G28" s="84">
+      <c r="G28" s="77">
         <f>E28*0.05</f>
         <v>1200</v>
       </c>
-      <c r="H28" s="84">
+      <c r="H28" s="77">
         <f>E28*0.5</f>
         <v>12000</v>
       </c>
@@ -10730,18 +10828,21 @@
         <v>43200</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K28" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" s="87" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="38" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C29" s="39">
         <v>1</v>
@@ -10749,19 +10850,19 @@
       <c r="D29" s="40">
         <v>2000</v>
       </c>
-      <c r="E29" s="84">
+      <c r="E29" s="77">
         <f>C29*D29*12</f>
         <v>24000</v>
       </c>
-      <c r="F29" s="84">
+      <c r="F29" s="77">
         <f>E29*Assumptions!B37</f>
         <v>6000</v>
       </c>
-      <c r="G29" s="84">
+      <c r="G29" s="77">
         <f>E29*0.05</f>
         <v>1200</v>
       </c>
-      <c r="H29" s="84">
+      <c r="H29" s="77">
         <f>E29*0.5</f>
         <v>12000</v>
       </c>
@@ -10770,18 +10871,21 @@
         <v>43200</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K29" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" s="87" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="38" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="C30" s="39">
         <v>1</v>
@@ -10789,19 +10893,19 @@
       <c r="D30" s="40">
         <v>2000</v>
       </c>
-      <c r="E30" s="85">
+      <c r="E30" s="78">
         <f>C30*D30*12</f>
         <v>24000</v>
       </c>
-      <c r="F30" s="85">
+      <c r="F30" s="78">
         <f>E30*Assumptions!B37</f>
         <v>6000</v>
       </c>
-      <c r="G30" s="85">
+      <c r="G30" s="78">
         <f>E30*0.05</f>
         <v>1200</v>
       </c>
-      <c r="H30" s="85">
+      <c r="H30" s="78">
         <f>E30*0.5</f>
         <v>12000</v>
       </c>
@@ -10810,18 +10914,21 @@
         <v>43200</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K30" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" s="87" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="38" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C31" s="39">
         <v>1</v>
@@ -10850,16 +10957,19 @@
         <v>38880</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K31" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" s="87" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="17"/>
       <c r="B32" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C32" s="41">
         <f>SUM(C28:C31)</f>
@@ -10876,28 +10986,30 @@
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="78" t="s">
-        <v>522</v>
-      </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="81" t="s">
+        <v>535</v>
+      </c>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="75"/>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="C34" s="39">
         <v>25</v>
@@ -10925,18 +11037,19 @@
         <v>234000</v>
       </c>
       <c r="J34" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K34" s="38" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" s="38"/>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="C35" s="39">
         <v>5</v>
@@ -10964,18 +11077,19 @@
         <v>117000</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K35" s="38" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" s="38"/>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="C36" s="39">
         <v>3</v>
@@ -11003,18 +11117,19 @@
         <v>56160</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="L36" s="38"/>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="C37" s="39">
         <v>1</v>
@@ -11042,18 +11157,19 @@
         <v>23400</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>513</v>
+      </c>
+      <c r="L37" s="38"/>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="C38" s="39">
         <v>3</v>
@@ -11081,18 +11197,19 @@
         <v>37440</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K38" s="38" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" s="38"/>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="C39" s="39">
         <v>4</v>
@@ -11120,18 +11237,19 @@
         <v>31200</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K39" s="38" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" s="38"/>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="C40" s="39">
         <v>2</v>
@@ -11159,18 +11277,19 @@
         <v>12480</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K40" s="38" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" s="38"/>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="38" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C41" s="39">
         <v>1</v>
@@ -11198,16 +11317,17 @@
         <v>23400</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K41" s="38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" s="38"/>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="17"/>
       <c r="B42" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C42" s="41">
         <f>SUM(C34:C41)</f>
@@ -11224,28 +11344,30 @@
       </c>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="78" t="s">
-        <v>532</v>
-      </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L42" s="19"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="81" t="s">
+        <v>545</v>
+      </c>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="75"/>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="38" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C44" s="39">
         <v>50</v>
@@ -11272,16 +11394,17 @@
         <v>189000</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>548</v>
+      </c>
+      <c r="L44" s="38"/>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="17"/>
       <c r="B45" s="17" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C45" s="41">
         <f>SUM(C44:C44)</f>
@@ -11298,11 +11421,12 @@
       </c>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L45" s="19"/>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="35"/>
       <c r="B47" s="35" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="C47" s="42">
         <f>C10+C18+C22+C26+C32+C42+C45</f>
@@ -11319,15 +11443,16 @@
       </c>
       <c r="J47" s="36"/>
       <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="62" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="62" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -11340,6 +11465,18 @@
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A27:K27"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L7" r:id="rId1" xr:uid="{037E2B71-E73F-43D7-8F05-7425B9E0DA77}"/>
+    <hyperlink ref="L29" r:id="rId2" xr:uid="{9800BA5D-00A2-4418-AB5D-67FCF70B0D98}"/>
+    <hyperlink ref="L28" r:id="rId3" xr:uid="{B2B9C213-7082-429A-BF3C-D766229BDFFA}"/>
+    <hyperlink ref="L30" r:id="rId4" xr:uid="{1E7DD607-9106-4CE5-8FDE-136D8056E128}"/>
+    <hyperlink ref="L31" r:id="rId5" xr:uid="{36E123EF-F596-42DC-931B-1935569DFF78}"/>
+    <hyperlink ref="L8" r:id="rId6" xr:uid="{C7957586-5554-435C-A060-58886048E155}"/>
+    <hyperlink ref="L6" r:id="rId7" xr:uid="{32E02B1A-87B2-46F9-8304-B0F005BC881A}"/>
+    <hyperlink ref="L4" r:id="rId8" xr:uid="{6B36DF8D-E14D-4F01-8729-719BC26B445A}"/>
+    <hyperlink ref="L3" r:id="rId9" xr:uid="{DFA8DFCF-7CDC-4958-BF08-7F03877FA36E}"/>
+    <hyperlink ref="L5" r:id="rId10" xr:uid="{1233851F-00B2-445B-AD54-E217982346BC}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -11365,52 +11502,52 @@
         <v>306</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="78" t="s">
-        <v>546</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="81" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="D3" s="43">
         <f>OPEX_HR!I47*0.55</f>
@@ -11437,7 +11574,7 @@
     <row r="4" spans="1:9">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="34">
@@ -11463,27 +11600,27 @@
       <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="78" t="s">
-        <v>551</v>
-      </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="A5" s="81" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="D6" s="2">
         <f>Assumptions!B10*Assumptions!B30</f>
@@ -11509,13 +11646,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="D7" s="2">
         <f>Assumptions!B20*Assumptions!B30</f>
@@ -11541,10 +11678,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>182</v>
@@ -11568,13 +11705,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="D9" s="2">
         <v>44000</v>
@@ -11595,13 +11732,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="D10" s="2">
         <v>18000</v>
@@ -11623,7 +11760,7 @@
     <row r="11" spans="1:9">
       <c r="A11" s="17"/>
       <c r="B11" s="17" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="34">
@@ -11649,27 +11786,27 @@
       <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="D13" s="2">
         <f>Assumptions!B16*Assumptions!B30</f>
@@ -11696,7 +11833,7 @@
     <row r="14" spans="1:9">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="34">
@@ -11722,24 +11859,24 @@
       <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="78" t="s">
-        <v>567</v>
-      </c>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
+      <c r="A15" s="81" t="s">
+        <v>580</v>
+      </c>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2">
@@ -11766,10 +11903,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2">
@@ -11796,10 +11933,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2">
@@ -11821,10 +11958,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2">
@@ -11846,10 +11983,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2">
@@ -11871,10 +12008,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2">
@@ -11896,10 +12033,10 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2">
@@ -11921,10 +12058,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2">
@@ -11947,7 +12084,7 @@
     <row r="24" spans="1:9">
       <c r="A24" s="17"/>
       <c r="B24" s="17" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="34">
@@ -11973,24 +12110,24 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="78" t="s">
-        <v>578</v>
-      </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
+      <c r="A25" s="81" t="s">
+        <v>591</v>
+      </c>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2">
@@ -12012,10 +12149,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2">
@@ -12037,10 +12174,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2">
@@ -12062,10 +12199,10 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2">
@@ -12087,10 +12224,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2">
@@ -12113,7 +12250,7 @@
     <row r="31" spans="1:9">
       <c r="A31" s="17"/>
       <c r="B31" s="17" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="34">
@@ -12139,24 +12276,24 @@
       <c r="I31" s="19"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="78" t="s">
-        <v>586</v>
-      </c>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
+      <c r="A32" s="81" t="s">
+        <v>599</v>
+      </c>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
         <v>313</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="2">
@@ -12181,7 +12318,7 @@
         <v>313</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2">
@@ -12204,7 +12341,7 @@
     <row r="35" spans="1:9">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="34">
@@ -12230,24 +12367,24 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="78" t="s">
-        <v>590</v>
-      </c>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
+      <c r="A36" s="81" t="s">
+        <v>603</v>
+      </c>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2">
@@ -12269,10 +12406,10 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2">
@@ -12294,10 +12431,10 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="2">
@@ -12319,10 +12456,10 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="2">
@@ -12344,10 +12481,10 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="2">
@@ -12370,7 +12507,7 @@
     <row r="42" spans="1:9">
       <c r="A42" s="17"/>
       <c r="B42" s="17" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="34">
@@ -12396,24 +12533,24 @@
       <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="78" t="s">
-        <v>597</v>
-      </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
+      <c r="A43" s="81" t="s">
+        <v>610</v>
+      </c>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2">
@@ -12435,10 +12572,10 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="2">
@@ -12460,10 +12597,10 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="2">
@@ -12485,10 +12622,10 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2">
@@ -12510,10 +12647,10 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="2">
@@ -12535,10 +12672,10 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="2">
@@ -12560,10 +12697,10 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="2">
@@ -12586,7 +12723,7 @@
     <row r="51" spans="1:9">
       <c r="A51" s="17"/>
       <c r="B51" s="17" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="34">
@@ -12614,7 +12751,7 @@
     <row r="53" spans="1:9">
       <c r="A53" s="35"/>
       <c r="B53" s="35" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="C53" s="36"/>
       <c r="D53" s="37">
@@ -12685,50 +12822,50 @@
         <v>308</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>101</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="78" t="s">
-        <v>613</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
+      <c r="A2" s="81" t="s">
+        <v>626</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="D3" s="1">
         <v>5</v>
@@ -12748,18 +12885,18 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>617</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="D4" s="1">
         <v>22</v>
@@ -12782,13 +12919,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="D5" s="1">
         <v>30</v>
@@ -12811,13 +12948,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="D6" s="1">
         <v>15</v>
@@ -12840,13 +12977,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="D7" s="1">
         <v>55</v>
@@ -12866,18 +13003,18 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -12900,13 +13037,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -12929,13 +13066,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="D10" s="1">
         <v>22</v>
@@ -12958,13 +13095,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="D11" s="1">
         <v>18</v>
@@ -12987,13 +13124,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="D12" s="1">
         <v>15</v>
@@ -13013,18 +13150,18 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>638</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -13047,13 +13184,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="D14" s="1">
         <v>22</v>
@@ -13076,13 +13213,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="D15" s="1">
         <v>30</v>
@@ -13105,13 +13242,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="D16" s="1">
         <v>22</v>
@@ -13134,13 +13271,13 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="D17" s="1">
         <v>37</v>
@@ -13166,10 +13303,10 @@
         <v>281</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="D18" s="1">
         <v>15</v>
@@ -13189,7 +13326,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -13197,10 +13334,10 @@
         <v>281</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="D19" s="1">
         <v>7</v>
@@ -13226,10 +13363,10 @@
         <v>281</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="D20" s="1">
         <v>30</v>
@@ -13249,7 +13386,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>654</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -13257,10 +13394,10 @@
         <v>281</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="D21" s="1">
         <v>0.75</v>
@@ -13280,13 +13417,13 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>657</v>
+        <v>670</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="17"/>
       <c r="B22" s="17" t="s">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -13309,7 +13446,7 @@
     <row r="23" spans="1:10">
       <c r="A23" s="44"/>
       <c r="B23" s="44" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="45"/>
@@ -13322,13 +13459,13 @@
       </c>
       <c r="I23" s="45"/>
       <c r="J23" s="45" t="s">
-        <v>660</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="35"/>
       <c r="B24" s="35" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
@@ -13343,9 +13480,9 @@
       <c r="J24" s="36"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75" t="s">
-        <v>662</v>
+      <c r="A25" s="76"/>
+      <c r="B25" s="76" t="s">
+        <v>675</v>
       </c>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
@@ -13358,27 +13495,27 @@
         <v>318780</v>
       </c>
       <c r="J25" s="63" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="78" t="s">
-        <v>664</v>
-      </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
+      <c r="A27" s="81" t="s">
+        <v>677</v>
+      </c>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -13394,16 +13531,16 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="E29" s="32">
         <v>50</v>
@@ -13422,16 +13559,16 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="E30" s="32">
         <v>30</v>
@@ -13450,14 +13587,14 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="E31" s="32">
         <v>10</v>
@@ -13479,13 +13616,13 @@
         <v>281</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>674</v>
+        <v>687</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="E32" s="32">
         <v>20</v>
@@ -13507,11 +13644,11 @@
         <v>281</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>677</v>
+        <v>690</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="E33" s="32">
         <v>10</v>
@@ -13533,13 +13670,13 @@
         <v>281</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>382</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>679</v>
+        <v>692</v>
       </c>
       <c r="E34" s="32">
         <v>24</v>
@@ -13559,7 +13696,7 @@
     <row r="35" spans="1:10">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
@@ -13582,7 +13719,7 @@
     <row r="36" spans="1:10">
       <c r="A36" s="44"/>
       <c r="B36" s="44" t="s">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
@@ -13599,7 +13736,7 @@
     <row r="37" spans="1:10">
       <c r="A37" s="57"/>
       <c r="B37" s="57" t="s">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
@@ -13614,18 +13751,18 @@
       <c r="J37" s="58"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="79" t="s">
-        <v>683</v>
-      </c>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="81"/>
+      <c r="A39" s="82" t="s">
+        <v>696</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="84"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="9"/>
@@ -13663,16 +13800,16 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>686</v>
+        <v>699</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>687</v>
+        <v>700</v>
       </c>
       <c r="E43" s="32">
         <v>5</v>
@@ -13693,21 +13830,21 @@
         <v>15600</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>688</v>
+        <v>701</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="E44" s="32">
         <v>1</v>
@@ -13731,16 +13868,16 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="E45" s="32">
         <v>1</v>
@@ -13761,21 +13898,21 @@
         <v>2340</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>693</v>
+        <v>706</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="E46" s="32">
         <v>1</v>
@@ -13796,21 +13933,21 @@
         <v>1872</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="E47" s="32">
         <v>1</v>
@@ -13831,21 +13968,21 @@
         <v>2808</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
@@ -13866,21 +14003,21 @@
         <v>4680</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>704</v>
+        <v>717</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -13888,13 +14025,13 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1" t="s">
-        <v>708</v>
+        <v>721</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="17"/>
       <c r="B50" s="17" t="s">
-        <v>709</v>
+        <v>722</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
@@ -13910,27 +14047,27 @@
         <v>29640</v>
       </c>
       <c r="J50" s="19" t="s">
-        <v>710</v>
+        <v>723</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="82" t="s">
-        <v>711</v>
-      </c>
-      <c r="B52" s="82"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82"/>
+      <c r="A52" s="85" t="s">
+        <v>724</v>
+      </c>
+      <c r="B52" s="85"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="85"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="85"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="9"/>
       <c r="B53" s="9" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
@@ -13947,7 +14084,7 @@
     <row r="54" spans="1:10">
       <c r="A54" s="9"/>
       <c r="B54" s="9" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -13964,7 +14101,7 @@
     <row r="55" spans="1:10">
       <c r="A55" s="9"/>
       <c r="B55" s="9" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
@@ -13981,7 +14118,7 @@
     <row r="56" spans="1:10">
       <c r="A56" s="57"/>
       <c r="B56" s="57" t="s">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="C56" s="58"/>
       <c r="D56" s="58"/>
@@ -14029,7 +14166,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="26" t="s">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="28"/>
@@ -14041,7 +14178,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="B2" s="47">
         <f>OPEX_Operations!F53/12</f>
@@ -14050,7 +14187,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="B3" s="47">
         <f>(Assumptions!B40+Assumptions!B41+Assumptions!B42)/12</f>
@@ -14059,39 +14196,39 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="B4" s="48">
         <v>0.14000000000000001</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.85">
       <c r="A6" s="15" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>311</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>720</v>
+        <v>733</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>721</v>
+        <v>734</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>724</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -14099,7 +14236,7 @@
         <v>321</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -14121,15 +14258,15 @@
         <v>-47209.537666666671</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>726</v>
+        <v>739</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -14151,7 +14288,7 @@
         <v>-94419.075333333341</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -14159,7 +14296,7 @@
         <v>370</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="C9" s="16">
         <v>0.05</v>
@@ -14181,7 +14318,7 @@
         <v>-91628.613000000012</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>729</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -14189,7 +14326,7 @@
         <v>426</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="C10" s="16">
         <v>0.08</v>
@@ -14211,15 +14348,15 @@
         <v>-58838.150666666683</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>730</v>
+        <v>743</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="C11" s="16">
         <v>0.1</v>
@@ -14241,15 +14378,15 @@
         <v>-6047.6883333333535</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>731</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="C12" s="16">
         <v>0.12</v>
@@ -14271,15 +14408,15 @@
         <v>66742.773999999976</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>732</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>733</v>
+        <v>746</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="C13" s="16">
         <v>0.12</v>
@@ -14301,7 +14438,7 @@
         <v>139533.23633333331</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14309,7 +14446,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="C14" s="16">
         <v>0.15</v>
@@ -14331,15 +14468,15 @@
         <v>238951.58883333331</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>737</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="C15" s="16">
         <v>0.25</v>
@@ -14361,7 +14498,7 @@
         <v>404648.84299999999</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>739</v>
+        <v>752</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -14369,7 +14506,7 @@
         <v>428</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="C16" s="16">
         <v>0.35</v>
@@ -14391,15 +14528,15 @@
         <v>636624.99883333337</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>740</v>
+        <v>753</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>741</v>
+        <v>754</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="C17" s="16">
         <v>0.42</v>
@@ -14421,7 +14558,7 @@
         <v>914996.38583333336</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>742</v>
+        <v>755</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -14429,7 +14566,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="C18" s="16">
         <v>0.48</v>
@@ -14451,15 +14588,15 @@
         <v>1233135.1138333334</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>743</v>
+        <v>756</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C19" s="16">
         <v>0.52</v>
@@ -14481,15 +14618,15 @@
         <v>1577785.4025000001</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>746</v>
+        <v>759</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C20" s="16">
         <v>0.55000000000000004</v>
@@ -14511,15 +14648,15 @@
         <v>1942319.3616666668</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>748</v>
+        <v>761</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C21" s="16">
         <v>0.57999999999999996</v>
@@ -14541,15 +14678,15 @@
         <v>2326736.9913333333</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>750</v>
+        <v>763</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C22" s="16">
         <v>0.62</v>
@@ -14571,15 +14708,15 @@
         <v>2737666.1816666666</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>752</v>
+        <v>765</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C23" s="16">
         <v>0.66</v>
@@ -14601,15 +14738,15 @@
         <v>3175106.9326666668</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>754</v>
+        <v>767</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>755</v>
+        <v>768</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="C24" s="16">
         <v>0.7</v>
@@ -14631,15 +14768,15 @@
         <v>3639059.2443333333</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>756</v>
+        <v>769</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C25" s="16">
         <v>0.74</v>
@@ -14661,15 +14798,15 @@
         <v>4129523.1166666667</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>759</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>760</v>
+        <v>773</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C26" s="16">
         <v>0.78</v>
@@ -14691,15 +14828,15 @@
         <v>4646498.5496666664</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>761</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C27" s="16">
         <v>0.82</v>
@@ -14721,15 +14858,15 @@
         <v>5189985.543333333</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>763</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C28" s="16">
         <v>0.86</v>
@@ -14751,15 +14888,15 @@
         <v>5759984.0976666659</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>765</v>
+        <v>778</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>766</v>
+        <v>779</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C29" s="16">
         <v>0.9</v>
@@ -14781,7 +14918,7 @@
         <v>6356494.2126666661</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>767</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -14789,7 +14926,7 @@
         <v>452</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C30" s="16">
         <v>0.95</v>
@@ -14811,34 +14948,34 @@
         <v>6986143.7785</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="78" t="s">
-        <v>769</v>
-      </c>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="A32" s="81" t="s">
+        <v>782</v>
+      </c>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
       <c r="J32" s="72" t="s">
-        <v>770</v>
+        <v>783</v>
       </c>
       <c r="K32" s="72" t="s">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="L32" s="72" t="s">
-        <v>772</v>
+        <v>785</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="35"/>
       <c r="B33" s="35" t="s">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -14850,19 +14987,19 @@
       </c>
       <c r="H33" s="36"/>
       <c r="J33" s="67" t="s">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="K33" s="68" t="s">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="L33" s="68" t="s">
-        <v>776</v>
+        <v>789</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="35"/>
       <c r="B34" s="35" t="s">
-        <v>777</v>
+        <v>790</v>
       </c>
       <c r="C34" s="36"/>
       <c r="D34" s="36"/>
@@ -14873,22 +15010,22 @@
         <v>25</v>
       </c>
       <c r="H34" s="36" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="J34" s="67" t="s">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="K34" s="68" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="L34" s="68" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="26"/>
       <c r="B35" s="26" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
@@ -14900,19 +15037,19 @@
       </c>
       <c r="H35" s="28"/>
       <c r="J35" s="67" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="K35" s="67" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="L35" s="68" t="s">
-        <v>785</v>
+        <v>798</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="51"/>
       <c r="B36" s="51" t="s">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="C36" s="52"/>
       <c r="D36" s="52"/>
@@ -14923,22 +15060,22 @@
         <v>2266057.8080000002</v>
       </c>
       <c r="H36" s="52" t="s">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="J36" s="69" t="s">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="K36" s="70">
         <v>25</v>
       </c>
       <c r="L36" s="71" t="s">
-        <v>789</v>
+        <v>802</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="51"/>
       <c r="B37" s="51" t="s">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="C37" s="52"/>
       <c r="D37" s="52"/>
@@ -14949,21 +15086,21 @@
         <v>24.000000000000004</v>
       </c>
       <c r="H37" s="52" t="s">
-        <v>791</v>
+        <v>804</v>
       </c>
       <c r="I37" s="66"/>
     </row>
     <row r="39" spans="1:12" ht="22.35" customHeight="1">
-      <c r="A39" s="75"/>
-      <c r="B39" s="83" t="s">
-        <v>792</v>
-      </c>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="86" t="s">
+        <v>805</v>
+      </c>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="86"/>
+      <c r="F39" s="86"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="2">
